--- a/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 24,55</t>
+          <t>-14,46; 24,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 24,82</t>
+          <t>-15,11; 23,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 28,86</t>
+          <t>-12,22; 26,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 29,94</t>
+          <t>-7,13; 31,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 12,86</t>
+          <t>-25,25; 13,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 18,22</t>
+          <t>-22,62; 17,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 22,06</t>
+          <t>-4,76; 22,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 14,45</t>
+          <t>-13,65; 13,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 18,08</t>
+          <t>-11,66; 16,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 115,02</t>
+          <t>-35,41; 115,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 108,15</t>
+          <t>-36,76; 102,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,57; 134,9</t>
+          <t>-30,37; 121,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 160,66</t>
+          <t>-16,9; 159,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,66; 67,15</t>
+          <t>-65,86; 73,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,39; 100,15</t>
+          <t>-57,27; 90,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 95,56</t>
+          <t>-12,77; 91,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 58,0</t>
+          <t>-36,96; 57,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 73,59</t>
+          <t>-32,13; 65,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 35,67</t>
+          <t>5,78; 37,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 25,11</t>
+          <t>-5,55; 23,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 33,45</t>
+          <t>-4,54; 33,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 2,55</t>
+          <t>-30,67; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 8,07</t>
+          <t>-25,94; 8,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 14,56</t>
+          <t>-17,79; 15,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 15,31</t>
+          <t>-7,7; 17,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 11,87</t>
+          <t>-10,43; 11,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 19,11</t>
+          <t>-5,72; 20,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,17; 197,9</t>
+          <t>15,53; 231,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 147,73</t>
+          <t>-15,62; 136,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 178,51</t>
+          <t>-13,13; 188,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 7,55</t>
+          <t>-53,32; 12,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 21,15</t>
+          <t>-46,53; 20,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 38,26</t>
+          <t>-31,2; 39,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 48,51</t>
+          <t>-18,18; 61,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 39,06</t>
+          <t>-24,09; 36,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 61,08</t>
+          <t>-13,25; 65,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 22,56</t>
+          <t>-13,91; 24,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 24,91</t>
+          <t>-13,87; 25,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 28,4</t>
+          <t>-34,5; 30,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 13,32</t>
+          <t>-21,92; 12,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 17,39</t>
+          <t>-17,37; 18,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 19,91</t>
+          <t>-15,1; 21,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 12,19</t>
+          <t>-14,13; 10,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 15,18</t>
+          <t>-12,15; 16,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 17,32</t>
+          <t>-22,02; 15,96</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 94,8</t>
+          <t>-31,38; 101,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 105,75</t>
+          <t>-31,03; 112,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 93,11</t>
+          <t>-63,6; 102,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 37,36</t>
+          <t>-41,69; 36,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 48,59</t>
+          <t>-33,22; 51,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 56,4</t>
+          <t>-28,2; 64,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 37,56</t>
+          <t>-29,91; 29,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 46,32</t>
+          <t>-25,2; 49,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,45; 47,73</t>
+          <t>-45,28; 43,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 16,8</t>
+          <t>-24,79; 17,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 18,41</t>
+          <t>-20,88; 19,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 24,18</t>
+          <t>-20,02; 24,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 17,94</t>
+          <t>-15,08; 18,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 13,49</t>
+          <t>-21,09; 14,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 28,94</t>
+          <t>-8,91; 29,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 12,04</t>
+          <t>-12,77; 13,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 11,6</t>
+          <t>-15,19; 12,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 19,92</t>
+          <t>-9,0; 21,11</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 56,0</t>
+          <t>-41,4; 59,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 60,26</t>
+          <t>-38,45; 69,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 79,17</t>
+          <t>-35,67; 78,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,26; 65,92</t>
+          <t>-32,98; 61,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,2; 45,71</t>
+          <t>-45,34; 48,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 98,87</t>
+          <t>-19,34; 98,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,53; 35,89</t>
+          <t>-26,73; 45,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 36,44</t>
+          <t>-32,13; 37,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 60,2</t>
+          <t>-18,63; 61,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 17,1</t>
+          <t>0,06; 17,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 14,89</t>
+          <t>-3,73; 15,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 18,9</t>
+          <t>-10,11; 20,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 6,09</t>
+          <t>-11,77; 6,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 4,46</t>
+          <t>-14,47; 4,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 11,28</t>
+          <t>-6,63; 12,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 8,71</t>
+          <t>-2,91; 9,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 7,25</t>
+          <t>-6,22; 6,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 12,08</t>
+          <t>-5,59; 11,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 61,31</t>
+          <t>0,13; 65,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 55,65</t>
+          <t>-10,11; 53,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 61,75</t>
+          <t>-27,65; 68,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 16,34</t>
+          <t>-25,37; 19,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 12,07</t>
+          <t>-30,94; 12,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 30,75</t>
+          <t>-14,43; 33,96</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 25,23</t>
+          <t>-7,25; 29,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 20,67</t>
+          <t>-15,27; 19,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 34,82</t>
+          <t>-13,95; 34,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 24,32</t>
+          <t>-13,39; 23,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 23,4</t>
+          <t>-15,57; 23,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 26,93</t>
+          <t>-11,21; 28,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 31,1</t>
+          <t>-7,48; 30,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 13,66</t>
+          <t>-26,07; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 17,98</t>
+          <t>-19,15; 19,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 22,6</t>
+          <t>-3,96; 22,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 13,86</t>
+          <t>-14,59; 13,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 16,96</t>
+          <t>-11,26; 17,44</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,41; 115,14</t>
+          <t>-33,15; 105,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 102,04</t>
+          <t>-36,17; 109,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 121,84</t>
+          <t>-26,43; 140,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 159,32</t>
+          <t>-16,9; 166,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 73,41</t>
+          <t>-69,15; 69,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,27; 90,54</t>
+          <t>-50,85; 102,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 91,59</t>
+          <t>-11,2; 94,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 57,81</t>
+          <t>-38,75; 57,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 65,55</t>
+          <t>-29,75; 71,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 37,34</t>
+          <t>7,77; 36,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 23,28</t>
+          <t>-3,42; 24,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 33,78</t>
+          <t>-5,18; 30,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 4,8</t>
+          <t>-29,33; 3,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,94; 8,03</t>
+          <t>-26,21; 8,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 15,06</t>
+          <t>-19,37; 15,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 17,64</t>
+          <t>-7,3; 15,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 11,58</t>
+          <t>-9,59; 12,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 20,12</t>
+          <t>-5,42; 18,91</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 231,8</t>
+          <t>21,58; 202,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 136,99</t>
+          <t>-12,38; 132,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 188,26</t>
+          <t>-14,78; 162,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,32; 12,87</t>
+          <t>-53,24; 9,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 20,01</t>
+          <t>-46,33; 21,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 39,87</t>
+          <t>-34,26; 42,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 61,1</t>
+          <t>-16,91; 51,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 36,95</t>
+          <t>-22,58; 40,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 65,31</t>
+          <t>-13,1; 61,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 24,65</t>
+          <t>-15,38; 22,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 25,89</t>
+          <t>-15,57; 24,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 30,4</t>
+          <t>-35,05; 28,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 12,12</t>
+          <t>-23,82; 10,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 18,16</t>
+          <t>-19,88; 17,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 21,63</t>
+          <t>-16,04; 21,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 10,46</t>
+          <t>-13,53; 12,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 16,08</t>
+          <t>-11,26; 15,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,02; 15,96</t>
+          <t>-24,83; 16,65</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 101,83</t>
+          <t>-32,41; 93,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 112,02</t>
+          <t>-31,68; 100,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,6; 102,11</t>
+          <t>-68,83; 93,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 36,37</t>
+          <t>-43,09; 31,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 51,46</t>
+          <t>-38,06; 52,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 64,53</t>
+          <t>-30,26; 60,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 29,87</t>
+          <t>-27,11; 37,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 49,65</t>
+          <t>-23,45; 46,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,28; 43,3</t>
+          <t>-50,41; 45,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 17,69</t>
+          <t>-21,77; 17,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 19,07</t>
+          <t>-24,54; 19,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 24,3</t>
+          <t>-18,1; 23,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 18,39</t>
+          <t>-16,98; 17,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 14,83</t>
+          <t>-22,15; 14,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 29,91</t>
+          <t>-10,2; 29,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 13,81</t>
+          <t>-12,86; 12,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 12,21</t>
+          <t>-15,37; 11,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 21,11</t>
+          <t>-8,31; 20,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 59,99</t>
+          <t>-39,41; 57,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 69,08</t>
+          <t>-41,98; 63,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 78,48</t>
+          <t>-32,54; 78,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 61,94</t>
+          <t>-36,79; 54,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 48,74</t>
+          <t>-46,82; 50,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 98,73</t>
+          <t>-22,93; 103,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 45,72</t>
+          <t>-27,47; 39,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 37,38</t>
+          <t>-32,08; 34,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 61,68</t>
+          <t>-17,77; 63,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 17,94</t>
+          <t>-0,03; 17,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 15,16</t>
+          <t>-3,18; 14,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 20,0</t>
+          <t>-11,52; 18,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 6,82</t>
+          <t>-10,18; 8,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 4,24</t>
+          <t>-14,51; 4,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 12,18</t>
+          <t>-8,29; 11,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 9,81</t>
+          <t>-3,6; 9,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,66</t>
+          <t>-5,94; 6,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 11,91</t>
+          <t>-5,9; 12,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,13; 65,25</t>
+          <t>-0,2; 63,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 53,88</t>
+          <t>-8,35; 50,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 68,1</t>
+          <t>-29,72; 63,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 19,21</t>
+          <t>-22,33; 22,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 12,8</t>
+          <t>-31,73; 11,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 33,96</t>
+          <t>-18,43; 32,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 29,15</t>
+          <t>-8,95; 27,49</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 19,2</t>
+          <t>-14,66; 20,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 34,71</t>
+          <t>-13,6; 35,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-6,5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,15</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-6,5</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 23,87</t>
+          <t>-5,02; 29,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 23,46</t>
+          <t>-25,04; 12,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 28,73</t>
+          <t>-19,81; 20,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 30,73</t>
+          <t>-14,46; 24,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 13,39</t>
+          <t>-15,42; 24,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 19,31</t>
+          <t>-11,64; 30,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 22,97</t>
+          <t>-3,59; 22,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 13,07</t>
+          <t>-14,58; 14,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 17,44</t>
+          <t>-9,3; 20,37</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-21,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-2,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>17,3%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>14,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-21,51%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,04%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 105,01</t>
+          <t>-11,93; 160,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 109,32</t>
+          <t>-65,66; 67,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 140,98</t>
+          <t>-50,07; 111,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 166,24</t>
+          <t>-35,4; 115,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 69,18</t>
+          <t>-38,57; 108,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 102,18</t>
+          <t>-27,83; 140,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 94,18</t>
+          <t>-9,58; 95,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 57,41</t>
+          <t>-39,32; 58,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 71,84</t>
+          <t>-25,48; 82,33</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-13,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-8,12</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>22,09</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10,23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-13,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,12</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,01</t>
+          <t>17,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,26</t>
+          <t>8,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 36,49</t>
+          <t>-29,67; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 24,42</t>
+          <t>-24,81; 8,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 30,86</t>
+          <t>-18,35; 15,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 3,41</t>
+          <t>5,63; 35,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 8,88</t>
+          <t>-4,65; 25,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 15,68</t>
+          <t>0,6; 34,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 15,69</t>
+          <t>-6,99; 15,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 12,57</t>
+          <t>-10,27; 11,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 18,91</t>
+          <t>-3,33; 20,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-27,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-16,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-3,08%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>87,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>40,36%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-27,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,83%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,17%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,58; 202,1</t>
+          <t>-51,98; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 132,81</t>
+          <t>-44,59; 21,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 162,12</t>
+          <t>-32,54; 39,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 9,1</t>
+          <t>15,17; 197,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 21,83</t>
+          <t>-14,69; 147,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 42,54</t>
+          <t>0,73; 196,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 51,82</t>
+          <t>-16,91; 48,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 40,77</t>
+          <t>-24,94; 39,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 61,39</t>
+          <t>-8,66; 63,5</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,37</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,82</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,03</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>21,39</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>9,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 22,24</t>
+          <t>-20,49; 13,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 24,75</t>
+          <t>-19,61; 17,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-35,05; 28,79</t>
+          <t>-18,66; 17,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 10,75</t>
+          <t>-13,58; 22,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 17,73</t>
+          <t>-13,61; 24,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 21,41</t>
+          <t>0,17; 40,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 12,36</t>
+          <t>-13,22; 12,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 15,03</t>
+          <t>-12,04; 15,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 16,65</t>
+          <t>-5,14; 23,41</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-11,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0,83%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-0,97%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>13,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>16,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-11,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-0,83%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,41; 93,1</t>
+          <t>-38,95; 37,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 100,31</t>
+          <t>-39,6; 48,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 93,45</t>
+          <t>-36,23; 49,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,09; 31,34</t>
+          <t>-29,9; 94,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 52,42</t>
+          <t>-30,4; 105,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 60,64</t>
+          <t>0,19; 169,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 37,56</t>
+          <t>-28,24; 37,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 46,86</t>
+          <t>-25,29; 46,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 45,57</t>
+          <t>-10,73; 71,26</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-3,36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11,06</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>7,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 17,28</t>
+          <t>-16,55; 17,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 19,11</t>
+          <t>-21,65; 13,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 23,68</t>
+          <t>-6,74; 30,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 17,1</t>
+          <t>-24,55; 16,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 14,31</t>
+          <t>-25,28; 18,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 29,58</t>
+          <t>-20,18; 24,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 12,71</t>
+          <t>-13,71; 12,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 11,68</t>
+          <t>-14,96; 11,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 20,67</t>
+          <t>-7,35; 21,59</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-8,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-6,19%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-4,26%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-8,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 57,06</t>
+          <t>-35,26; 65,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 63,95</t>
+          <t>-47,2; 45,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 78,48</t>
+          <t>-14,84; 104,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 54,85</t>
+          <t>-42,87; 56,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 50,74</t>
+          <t>-44,35; 60,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 103,83</t>
+          <t>-36,4; 78,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 39,05</t>
+          <t>-28,53; 35,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 34,17</t>
+          <t>-31,91; 36,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 63,19</t>
+          <t>-16,26; 64,39</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-2,21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-4,49</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,74</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>8,99</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,29</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-4,49</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>15,75</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>8,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 17,8</t>
+          <t>-10,88; 6,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 14,37</t>
+          <t>-13,99; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 18,84</t>
+          <t>-6,81; 11,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 8,12</t>
+          <t>-0,53; 17,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 4,43</t>
+          <t>-2,4; 14,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 11,47</t>
+          <t>5,79; 24,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,34</t>
+          <t>-3,55; 8,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 6,99</t>
+          <t>-5,98; 7,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 12,2</t>
+          <t>2,44; 15,27</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-5,36%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-10,89%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>27,29%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>17,41%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-5,36%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-10,89%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 63,21</t>
+          <t>-24,42; 16,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 50,83</t>
+          <t>-31,09; 12,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 63,66</t>
+          <t>-15,78; 31,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 22,71</t>
+          <t>-1,21; 61,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 11,69</t>
+          <t>-6,92; 55,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 32,37</t>
+          <t>16,42; 90,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 27,49</t>
+          <t>-8,5; 25,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 20,91</t>
+          <t>-14,85; 20,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 35,18</t>
+          <t>6,13; 46,06</t>
         </is>
       </c>
     </row>
